--- a/Results_experiment/exp_1/preds_1114422222322222.xlsx
+++ b/Results_experiment/exp_1/preds_1114422222322222.xlsx
@@ -1245,7 +1245,7 @@
         <v>-3</v>
       </c>
       <c r="D2">
-        <v>0.1234549283981323</v>
+        <v>-0.32404425740242</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1259,7 +1259,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D3">
-        <v>0.277534008026123</v>
+        <v>0.1888459920883179</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1273,7 +1273,7 @@
         <v>-3</v>
       </c>
       <c r="D4">
-        <v>-0.2349316477775574</v>
+        <v>-1.108514308929443</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1287,7 +1287,7 @@
         <v>-2.299999952316284</v>
       </c>
       <c r="D5">
-        <v>-0.7356927990913391</v>
+        <v>-0.7935860157012939</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1301,7 +1301,7 @@
         <v>-1.600000023841858</v>
       </c>
       <c r="D6">
-        <v>-3.481642961502075</v>
+        <v>-2.22363543510437</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1315,7 +1315,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D7">
-        <v>1.345809459686279</v>
+        <v>1.393007755279541</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1329,7 +1329,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D8">
-        <v>3.488908052444458</v>
+        <v>4.253863334655762</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1343,7 +1343,7 @@
         <v>-4.5</v>
       </c>
       <c r="D9">
-        <v>-0.9548878073692322</v>
+        <v>-0.1585777401924133</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1357,7 +1357,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D10">
-        <v>0.8274605870246887</v>
+        <v>0.9890071153640747</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1371,7 +1371,7 @@
         <v>7.199999809265137</v>
       </c>
       <c r="D11">
-        <v>1.258478045463562</v>
+        <v>1.096600294113159</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1385,7 +1385,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D12">
-        <v>1.970025539398193</v>
+        <v>1.15430748462677</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1399,7 +1399,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D13">
-        <v>0.5561692118644714</v>
+        <v>0.7771979570388794</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1413,7 +1413,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D14">
-        <v>-0.09237176179885864</v>
+        <v>-0.02619102597236633</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1427,7 +1427,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D15">
-        <v>2.725312232971191</v>
+        <v>1.980886340141296</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1441,7 +1441,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D16">
-        <v>-3.59393048286438</v>
+        <v>-3.574377536773682</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1455,7 +1455,7 @@
         <v>-0.2000000029802322</v>
       </c>
       <c r="D17">
-        <v>-0.005642056465148926</v>
+        <v>-0.03280346095561981</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1469,7 +1469,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D18">
-        <v>0.6779388189315796</v>
+        <v>0.3365563154220581</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1483,7 +1483,7 @@
         <v>-4.699999809265137</v>
       </c>
       <c r="D19">
-        <v>-1.174189567565918</v>
+        <v>-0.8345479965209961</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -1497,7 +1497,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D20">
-        <v>-0.140928328037262</v>
+        <v>0.117905393242836</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -1511,7 +1511,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D21">
-        <v>0.666938304901123</v>
+        <v>0.8813947439193726</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -1525,7 +1525,7 @@
         <v>7.099999904632568</v>
       </c>
       <c r="D22">
-        <v>3.284770488739014</v>
+        <v>3.114070653915405</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -1539,7 +1539,7 @@
         <v>-2.599999904632568</v>
       </c>
       <c r="D23">
-        <v>2.497695446014404</v>
+        <v>2.835993051528931</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -1553,7 +1553,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D24">
-        <v>0.4389033317565918</v>
+        <v>-0.9194610118865967</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -1567,7 +1567,7 @@
         <v>0.5</v>
       </c>
       <c r="D25">
-        <v>1.884669303894043</v>
+        <v>0.1752505898475647</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -1581,7 +1581,7 @@
         <v>-4.699999809265137</v>
       </c>
       <c r="D26">
-        <v>-2.28147292137146</v>
+        <v>-3.171695470809937</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -1595,7 +1595,7 @@
         <v>-2.200000047683716</v>
       </c>
       <c r="D27">
-        <v>0.8713692426681519</v>
+        <v>0.03623214364051819</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -1609,7 +1609,7 @@
         <v>-0.300000011920929</v>
       </c>
       <c r="D28">
-        <v>0.1175479888916016</v>
+        <v>0.1279734075069427</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -1623,7 +1623,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D29">
-        <v>0.8311442136764526</v>
+        <v>1.559448719024658</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -1637,7 +1637,7 @@
         <v>-1.200000047683716</v>
       </c>
       <c r="D30">
-        <v>-0.9240559935569763</v>
+        <v>-1.760244488716125</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -1651,7 +1651,7 @@
         <v>6.900000095367432</v>
       </c>
       <c r="D31">
-        <v>3.953195810317993</v>
+        <v>3.425940275192261</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -1665,7 +1665,7 @@
         <v>11.69999980926514</v>
       </c>
       <c r="D32">
-        <v>3.063514471054077</v>
+        <v>4.65761661529541</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -1679,7 +1679,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D33">
-        <v>0.7566133737564087</v>
+        <v>0.6094943284988403</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -1693,7 +1693,7 @@
         <v>-0.800000011920929</v>
       </c>
       <c r="D34">
-        <v>0.03151652216911316</v>
+        <v>-0.1198258399963379</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -1707,7 +1707,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D35">
-        <v>-1.358603477478027</v>
+        <v>-1.919095754623413</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -1721,7 +1721,7 @@
         <v>19.20000076293945</v>
       </c>
       <c r="D36">
-        <v>11.16053295135498</v>
+        <v>13.84079074859619</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -1735,7 +1735,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D37">
-        <v>1.161747694015503</v>
+        <v>1.069740176200867</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -1749,7 +1749,7 @@
         <v>-4.300000190734863</v>
       </c>
       <c r="D38">
-        <v>0.5235100984573364</v>
+        <v>-0.5826621055603027</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -1763,7 +1763,7 @@
         <v>6.199999809265137</v>
       </c>
       <c r="D39">
-        <v>2.877769470214844</v>
+        <v>2.058242082595825</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -1777,7 +1777,7 @@
         <v>-0.1000000014901161</v>
       </c>
       <c r="D40">
-        <v>0.1985088288784027</v>
+        <v>0.482450395822525</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -1791,7 +1791,7 @@
         <v>-1.799999952316284</v>
       </c>
       <c r="D41">
-        <v>0.3837100267410278</v>
+        <v>0.07558538019657135</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -1805,7 +1805,7 @@
         <v>12.89999961853027</v>
       </c>
       <c r="D42">
-        <v>3.072679758071899</v>
+        <v>3.605524778366089</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1819,7 +1819,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D43">
-        <v>0.7449826002120972</v>
+        <v>0.5482082366943359</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1833,7 +1833,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D44">
-        <v>3.864114999771118</v>
+        <v>3.290112733840942</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1847,7 +1847,7 @@
         <v>-0.1000000014901161</v>
       </c>
       <c r="D45">
-        <v>-0.2204524278640747</v>
+        <v>-0.2272442877292633</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1861,7 +1861,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D46">
-        <v>1.375326633453369</v>
+        <v>0.8829582929611206</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1875,7 +1875,7 @@
         <v>-1.899999976158142</v>
       </c>
       <c r="D47">
-        <v>0.5216559171676636</v>
+        <v>0.1620224416255951</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1889,7 +1889,7 @@
         <v>3.5</v>
       </c>
       <c r="D48">
-        <v>3.12805438041687</v>
+        <v>1.878129243850708</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1903,7 +1903,7 @@
         <v>-1.799999952316284</v>
       </c>
       <c r="D49">
-        <v>-4.32110071182251</v>
+        <v>-1.800274610519409</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1917,7 +1917,7 @@
         <v>-1.100000023841858</v>
       </c>
       <c r="D50">
-        <v>1.663706064224243</v>
+        <v>0.9345353841781616</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1931,7 +1931,7 @@
         <v>-2</v>
       </c>
       <c r="D51">
-        <v>0.4271661639213562</v>
+        <v>0.2711576223373413</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1945,7 +1945,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D52">
-        <v>1.322179317474365</v>
+        <v>1.736752867698669</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1959,7 +1959,7 @@
         <v>-7</v>
       </c>
       <c r="D53">
-        <v>-0.3348283767700195</v>
+        <v>-0.8819222450256348</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1973,7 +1973,7 @@
         <v>-2.5</v>
       </c>
       <c r="D54">
-        <v>-0.4917153120040894</v>
+        <v>-0.481609970331192</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1987,7 +1987,7 @@
         <v>-2.900000095367432</v>
       </c>
       <c r="D55">
-        <v>-0.7136519551277161</v>
+        <v>-1.459702730178833</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2001,7 +2001,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D56">
-        <v>2.082594871520996</v>
+        <v>2.360680341720581</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2015,7 +2015,7 @@
         <v>-10.19999980926514</v>
       </c>
       <c r="D57">
-        <v>-6.331112861633301</v>
+        <v>-7.218826293945312</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2029,7 +2029,7 @@
         <v>-1.399999976158142</v>
       </c>
       <c r="D58">
-        <v>0.5456492304801941</v>
+        <v>0.06910370290279388</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2043,7 +2043,7 @@
         <v>2.5</v>
       </c>
       <c r="D59">
-        <v>1.656594276428223</v>
+        <v>1.724849462509155</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2057,7 +2057,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D60">
-        <v>4.614669322967529</v>
+        <v>3.285335779190063</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2071,7 +2071,7 @@
         <v>-0.5</v>
       </c>
       <c r="D61">
-        <v>-0.4724916815757751</v>
+        <v>0.2342309057712555</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2085,7 +2085,7 @@
         <v>-7.599999904632568</v>
       </c>
       <c r="D62">
-        <v>-6.160098075866699</v>
+        <v>-6.388367652893066</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2099,7 +2099,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D63">
-        <v>0.628170371055603</v>
+        <v>0.2432351112365723</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2113,7 +2113,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D64">
-        <v>0.3191584348678589</v>
+        <v>0.2812455892562866</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2127,7 +2127,7 @@
         <v>-0.8999999761581421</v>
       </c>
       <c r="D65">
-        <v>-0.4651382565498352</v>
+        <v>-0.340482622385025</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2141,7 +2141,7 @@
         <v>-1.5</v>
       </c>
       <c r="D66">
-        <v>-1.304855108261108</v>
+        <v>-1.358254194259644</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2155,7 +2155,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D67">
-        <v>3.200952768325806</v>
+        <v>3.217170476913452</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2169,7 +2169,7 @@
         <v>5.5</v>
       </c>
       <c r="D68">
-        <v>2.990530252456665</v>
+        <v>2.813069581985474</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2183,7 +2183,7 @@
         <v>-1.200000047683716</v>
       </c>
       <c r="D69">
-        <v>1.336554050445557</v>
+        <v>1.336270570755005</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2197,7 +2197,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D70">
-        <v>-1.080595970153809</v>
+        <v>-0.5813982486724854</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2211,7 +2211,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D71">
-        <v>1.022353887557983</v>
+        <v>1.270207166671753</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2225,7 +2225,7 @@
         <v>3.5</v>
       </c>
       <c r="D72">
-        <v>3.954967975616455</v>
+        <v>4.567451953887939</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2239,7 +2239,7 @@
         <v>1</v>
       </c>
       <c r="D73">
-        <v>0.9754795432090759</v>
+        <v>0.7334327697753906</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2253,7 +2253,7 @@
         <v>-1.399999976158142</v>
       </c>
       <c r="D74">
-        <v>-0.5318984985351562</v>
+        <v>0.1074648350477219</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2267,7 +2267,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D75">
-        <v>5.072732925415039</v>
+        <v>3.846425294876099</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2281,7 +2281,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D76">
-        <v>0.0893130898475647</v>
+        <v>0.04836127161979675</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2295,7 +2295,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D77">
-        <v>1.86637282371521</v>
+        <v>2.579537153244019</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2309,7 +2309,7 @@
         <v>2</v>
       </c>
       <c r="D78">
-        <v>1.606184244155884</v>
+        <v>2.367719650268555</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2323,7 +2323,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D79">
-        <v>2.70136284828186</v>
+        <v>2.658507823944092</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2337,7 +2337,7 @@
         <v>-8.100000381469727</v>
       </c>
       <c r="D80">
-        <v>-0.2241062521934509</v>
+        <v>-0.4226271212100983</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2351,7 +2351,7 @@
         <v>7</v>
       </c>
       <c r="D81">
-        <v>2.233147144317627</v>
+        <v>2.295475959777832</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2365,7 +2365,7 @@
         <v>-1.700000047683716</v>
       </c>
       <c r="D82">
-        <v>0.1031259298324585</v>
+        <v>-0.01851160824298859</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2379,7 +2379,7 @@
         <v>-6.699999809265137</v>
       </c>
       <c r="D83">
-        <v>-3.828264474868774</v>
+        <v>-3.554580926895142</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -2393,7 +2393,7 @@
         <v>1</v>
       </c>
       <c r="D84">
-        <v>3.925417184829712</v>
+        <v>2.970046997070312</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -2407,7 +2407,7 @@
         <v>-21</v>
       </c>
       <c r="D85">
-        <v>-16.58285140991211</v>
+        <v>-15.1444787979126</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -2421,7 +2421,7 @@
         <v>-4.699999809265137</v>
       </c>
       <c r="D86">
-        <v>0.08137708902359009</v>
+        <v>0.06881387531757355</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -2435,7 +2435,7 @@
         <v>-0.8999999761581421</v>
       </c>
       <c r="D87">
-        <v>0.09011825919151306</v>
+        <v>-0.04440091550350189</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -2449,7 +2449,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D88">
-        <v>2.36617112159729</v>
+        <v>2.857853174209595</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -2463,7 +2463,7 @@
         <v>-3</v>
       </c>
       <c r="D89">
-        <v>1.30017352104187</v>
+        <v>0.4010490775108337</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -2477,7 +2477,7 @@
         <v>-1.899999976158142</v>
       </c>
       <c r="D90">
-        <v>1.850623607635498</v>
+        <v>2.050872087478638</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -2491,7 +2491,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D91">
-        <v>0.5103700160980225</v>
+        <v>0.587035059928894</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -2505,7 +2505,7 @@
         <v>-7.099999904632568</v>
       </c>
       <c r="D92">
-        <v>-0.854408323764801</v>
+        <v>-2.643786907196045</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -2519,7 +2519,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D93">
-        <v>1.492433071136475</v>
+        <v>1.102483153343201</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -2533,7 +2533,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D94">
-        <v>0.426393061876297</v>
+        <v>0.3164024353027344</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -2547,7 +2547,7 @@
         <v>-2</v>
       </c>
       <c r="D95">
-        <v>-0.8361347317695618</v>
+        <v>-0.3178587257862091</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -2561,7 +2561,7 @@
         <v>-1.5</v>
       </c>
       <c r="D96">
-        <v>0.5874322652816772</v>
+        <v>0.7887688875198364</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -2575,7 +2575,7 @@
         <v>3</v>
       </c>
       <c r="D97">
-        <v>1.823206424713135</v>
+        <v>2.506272077560425</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -2589,7 +2589,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D98">
-        <v>1.774937629699707</v>
+        <v>1.173359513282776</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -2603,7 +2603,7 @@
         <v>-0.1000000014901161</v>
       </c>
       <c r="D99">
-        <v>-0.05946230888366699</v>
+        <v>-0.2312513291835785</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -2617,7 +2617,7 @@
         <v>-0.5</v>
       </c>
       <c r="D100">
-        <v>0.1256367862224579</v>
+        <v>-0.08766141533851624</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -2631,7 +2631,7 @@
         <v>-1.5</v>
       </c>
       <c r="D101">
-        <v>0.7129619121551514</v>
+        <v>0.2318670749664307</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -2645,7 +2645,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D102">
-        <v>0.9103749394416809</v>
+        <v>1.729785561561584</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -2659,7 +2659,7 @@
         <v>11.89999961853027</v>
       </c>
       <c r="D103">
-        <v>4.895523548126221</v>
+        <v>6.418865203857422</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -2673,7 +2673,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D104">
-        <v>4.954147815704346</v>
+        <v>5.12208080291748</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -2687,7 +2687,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D105">
-        <v>2.13037633895874</v>
+        <v>3.5971519947052</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -2701,7 +2701,7 @@
         <v>2</v>
       </c>
       <c r="D106">
-        <v>-1.046136140823364</v>
+        <v>-0.08510890603065491</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -2715,7 +2715,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D107">
-        <v>1.166259288787842</v>
+        <v>1.122073769569397</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -2729,7 +2729,7 @@
         <v>2.5</v>
       </c>
       <c r="D108">
-        <v>1.080153703689575</v>
+        <v>1.142704844474792</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -2743,7 +2743,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D109">
-        <v>1.770103931427002</v>
+        <v>0.9973584413528442</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -2757,7 +2757,7 @@
         <v>11.10000038146973</v>
       </c>
       <c r="D110">
-        <v>5.275261402130127</v>
+        <v>6.936293601989746</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -2771,7 +2771,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D111">
-        <v>1.911992311477661</v>
+        <v>0.1298276335000992</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -2785,7 +2785,7 @@
         <v>-0.6000000238418579</v>
       </c>
       <c r="D112">
-        <v>-0.4611003994941711</v>
+        <v>-0.2124446332454681</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -2799,7 +2799,7 @@
         <v>-0.6000000238418579</v>
       </c>
       <c r="D113">
-        <v>0.4689232409000397</v>
+        <v>0.08062327653169632</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -2813,7 +2813,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D114">
-        <v>0.9115175604820251</v>
+        <v>0.04866132140159607</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -2827,7 +2827,7 @@
         <v>0.5</v>
       </c>
       <c r="D115">
-        <v>0.5437507629394531</v>
+        <v>0.1165911480784416</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -2841,7 +2841,7 @@
         <v>2</v>
       </c>
       <c r="D116">
-        <v>1.592541456222534</v>
+        <v>1.653665900230408</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -2855,7 +2855,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D117">
-        <v>0.2575532793998718</v>
+        <v>0.5120766162872314</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -2869,7 +2869,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D118">
-        <v>2.695050477981567</v>
+        <v>2.736043930053711</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -2883,7 +2883,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D119">
-        <v>0.7387274503707886</v>
+        <v>1.020827770233154</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -2897,7 +2897,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D120">
-        <v>1.524734020233154</v>
+        <v>1.231595754623413</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -2911,7 +2911,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D121">
-        <v>1.527979850769043</v>
+        <v>1.505194664001465</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -2925,7 +2925,7 @@
         <v>17.10000038146973</v>
       </c>
       <c r="D122">
-        <v>4.604232788085938</v>
+        <v>4.813671112060547</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -2939,7 +2939,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D123">
-        <v>2.080617189407349</v>
+        <v>1.320358276367188</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -2953,7 +2953,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D124">
-        <v>0.8091065883636475</v>
+        <v>1.203521728515625</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -2967,7 +2967,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D125">
-        <v>1.474713802337646</v>
+        <v>2.458907842636108</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -2981,7 +2981,7 @@
         <v>-18.29999923706055</v>
       </c>
       <c r="D126">
-        <v>-13.99631023406982</v>
+        <v>-12.74014759063721</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -2995,7 +2995,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D127">
-        <v>2.027860164642334</v>
+        <v>0.08259066194295883</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3009,7 +3009,7 @@
         <v>-1.200000047683716</v>
       </c>
       <c r="D128">
-        <v>-1.2374107837677</v>
+        <v>-1.187317371368408</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3023,7 +3023,7 @@
         <v>-1.299999952316284</v>
       </c>
       <c r="D129">
-        <v>0.09983235597610474</v>
+        <v>-0.05680075287818909</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3037,7 +3037,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D130">
-        <v>0.4969068169593811</v>
+        <v>0.09515528380870819</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3051,7 +3051,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D131">
-        <v>0.08408796787261963</v>
+        <v>0.2535502314567566</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3065,7 +3065,7 @@
         <v>-2.599999904632568</v>
       </c>
       <c r="D132">
-        <v>-1.608425378799438</v>
+        <v>-1.307407021522522</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3079,7 +3079,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D133">
-        <v>3.39480185508728</v>
+        <v>4.154809474945068</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3093,7 +3093,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D134">
-        <v>0.351727306842804</v>
+        <v>0.1400174200534821</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3107,7 +3107,7 @@
         <v>-0.300000011920929</v>
       </c>
       <c r="D135">
-        <v>-1.830405235290527</v>
+        <v>-2.114013433456421</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3121,7 +3121,7 @@
         <v>17.29999923706055</v>
       </c>
       <c r="D136">
-        <v>5.778089046478271</v>
+        <v>4.237404823303223</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3135,7 +3135,7 @@
         <v>2.5</v>
       </c>
       <c r="D137">
-        <v>1.940233469009399</v>
+        <v>1.10395872592926</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3149,7 +3149,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D138">
-        <v>1.386304378509521</v>
+        <v>0.9605308771133423</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3163,7 +3163,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D139">
-        <v>3.168493032455444</v>
+        <v>2.616093635559082</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3177,7 +3177,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D140">
-        <v>-0.02400347590446472</v>
+        <v>-1.732128143310547</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3191,7 +3191,7 @@
         <v>-2.200000047683716</v>
       </c>
       <c r="D141">
-        <v>2.954405069351196</v>
+        <v>2.307024002075195</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3205,7 +3205,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D142">
-        <v>3.005879402160645</v>
+        <v>4.448929786682129</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3219,7 +3219,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D143">
-        <v>1.211501598358154</v>
+        <v>2.525723457336426</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3233,7 +3233,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D144">
-        <v>1.558508157730103</v>
+        <v>0.9839357137680054</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3247,7 +3247,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D145">
-        <v>0.6976022124290466</v>
+        <v>0.5153821706771851</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3261,7 +3261,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D146">
-        <v>1.399770259857178</v>
+        <v>1.57368540763855</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3275,7 +3275,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D147">
-        <v>1.914173364639282</v>
+        <v>2.42609715461731</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3289,7 +3289,7 @@
         <v>-1.399999976158142</v>
       </c>
       <c r="D148">
-        <v>-1.399189949035645</v>
+        <v>-1.29140043258667</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3303,7 +3303,7 @@
         <v>-0.6000000238418579</v>
       </c>
       <c r="D149">
-        <v>0.7223023772239685</v>
+        <v>1.965319514274597</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3317,7 +3317,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D150">
-        <v>1.513226747512817</v>
+        <v>2.080440759658813</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3331,7 +3331,7 @@
         <v>-6.300000190734863</v>
       </c>
       <c r="D151">
-        <v>-3.033614158630371</v>
+        <v>-2.256417274475098</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3345,7 +3345,7 @@
         <v>-11</v>
       </c>
       <c r="D152">
-        <v>-8.251505851745605</v>
+        <v>-7.539024353027344</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3359,7 +3359,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D153">
-        <v>2.61356520652771</v>
+        <v>2.534102439880371</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3373,7 +3373,7 @@
         <v>-2.700000047683716</v>
       </c>
       <c r="D154">
-        <v>-0.1474651098251343</v>
+        <v>-0.1704841554164886</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -3387,7 +3387,7 @@
         <v>-0.1000000014901161</v>
       </c>
       <c r="D155">
-        <v>0.7499819397926331</v>
+        <v>0.5628036260604858</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -3401,7 +3401,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D156">
-        <v>0.5701467990875244</v>
+        <v>0.2805246710777283</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -3415,7 +3415,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D157">
-        <v>1.034149646759033</v>
+        <v>1.160958528518677</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -3429,7 +3429,7 @@
         <v>-0.6000000238418579</v>
       </c>
       <c r="D158">
-        <v>3.18561315536499</v>
+        <v>3.452858209609985</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -3443,7 +3443,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D159">
-        <v>0.05757588148117065</v>
+        <v>-0.1380326449871063</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -3457,7 +3457,7 @@
         <v>-5.199999809265137</v>
       </c>
       <c r="D160">
-        <v>-0.6665579676628113</v>
+        <v>-0.3205458223819733</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -3471,7 +3471,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D161">
-        <v>1.56759786605835</v>
+        <v>1.806318640708923</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -3485,7 +3485,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D162">
-        <v>-2.817875146865845</v>
+        <v>-1.312782526016235</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -3499,7 +3499,7 @@
         <v>1.5</v>
       </c>
       <c r="D163">
-        <v>-0.0477314293384552</v>
+        <v>0.7202850580215454</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -3513,7 +3513,7 @@
         <v>0.5</v>
       </c>
       <c r="D164">
-        <v>1.530754089355469</v>
+        <v>-0.227918952703476</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -3527,7 +3527,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D165">
-        <v>0.9853020310401917</v>
+        <v>1.276457905769348</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -3541,7 +3541,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D166">
-        <v>2.117648601531982</v>
+        <v>2.116564750671387</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -3555,7 +3555,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D167">
-        <v>1.326482653617859</v>
+        <v>2.395746946334839</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -3569,7 +3569,7 @@
         <v>-2.900000095367432</v>
       </c>
       <c r="D168">
-        <v>0.6630754470825195</v>
+        <v>-0.03930021822452545</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -3583,7 +3583,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D169">
-        <v>0.4750344157218933</v>
+        <v>0.4467377066612244</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -3597,7 +3597,7 @@
         <v>-6</v>
       </c>
       <c r="D170">
-        <v>-1.885831832885742</v>
+        <v>-1.714474201202393</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -3611,7 +3611,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D171">
-        <v>1.158761978149414</v>
+        <v>1.838876724243164</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -3625,7 +3625,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D172">
-        <v>0.1732631325721741</v>
+        <v>0.8987694978713989</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -3639,7 +3639,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D173">
-        <v>2.697278738021851</v>
+        <v>1.46459698677063</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -3653,7 +3653,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D174">
-        <v>0.6680142879486084</v>
+        <v>0.4824541509151459</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -3667,7 +3667,7 @@
         <v>2.5</v>
       </c>
       <c r="D175">
-        <v>2.440830945968628</v>
+        <v>2.941960334777832</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -3681,7 +3681,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D176">
-        <v>0.7683867216110229</v>
+        <v>0.4689750969409943</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -3695,7 +3695,7 @@
         <v>-1.299999952316284</v>
       </c>
       <c r="D177">
-        <v>0.1848167926073074</v>
+        <v>0.7822896242141724</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -3709,7 +3709,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D178">
-        <v>0.5822353363037109</v>
+        <v>1.623253345489502</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -3723,7 +3723,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D179">
-        <v>3.488876104354858</v>
+        <v>2.761816263198853</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -3737,7 +3737,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D180">
-        <v>0.1773968189954758</v>
+        <v>0.2190959602594376</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -3751,7 +3751,7 @@
         <v>-0.300000011920929</v>
       </c>
       <c r="D181">
-        <v>0.05260568857192993</v>
+        <v>0.02947157621383667</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -3765,7 +3765,7 @@
         <v>-0.300000011920929</v>
       </c>
       <c r="D182">
-        <v>-0.9432321190834045</v>
+        <v>-0.2105802595615387</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -3779,7 +3779,7 @@
         <v>-0.5</v>
       </c>
       <c r="D183">
-        <v>-1.211491346359253</v>
+        <v>-0.5379115343093872</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -3793,7 +3793,7 @@
         <v>5</v>
       </c>
       <c r="D184">
-        <v>1.846969127655029</v>
+        <v>2.603290557861328</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -3807,7 +3807,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D185">
-        <v>0.9318345189094543</v>
+        <v>1.90605092048645</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -3821,7 +3821,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D186">
-        <v>1.443002462387085</v>
+        <v>1.352885127067566</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -3835,7 +3835,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D187">
-        <v>0.09777423739433289</v>
+        <v>0.07601103186607361</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -3849,7 +3849,7 @@
         <v>-1.399999976158142</v>
       </c>
       <c r="D188">
-        <v>0.004845380783081055</v>
+        <v>0.05768296122550964</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -3863,7 +3863,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D189">
-        <v>0.02586981654167175</v>
+        <v>0.9981783628463745</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -3877,7 +3877,7 @@
         <v>6</v>
       </c>
       <c r="D190">
-        <v>2.059486865997314</v>
+        <v>2.097491979598999</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -3891,7 +3891,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D191">
-        <v>3.257894277572632</v>
+        <v>3.938138246536255</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -3905,7 +3905,7 @@
         <v>-0.1000000014901161</v>
       </c>
       <c r="D192">
-        <v>-0.1477667689323425</v>
+        <v>-0.007729873061180115</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -3919,7 +3919,7 @@
         <v>1.5</v>
       </c>
       <c r="D193">
-        <v>1.474339962005615</v>
+        <v>1.147081971168518</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -3933,7 +3933,7 @@
         <v>-0.8999999761581421</v>
       </c>
       <c r="D194">
-        <v>0.2116639912128448</v>
+        <v>0.121311642229557</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -3947,7 +3947,7 @@
         <v>-0.300000011920929</v>
       </c>
       <c r="D195">
-        <v>2.091448068618774</v>
+        <v>2.544916391372681</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -3961,7 +3961,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D196">
-        <v>1.182967185974121</v>
+        <v>0.735348105430603</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -3975,7 +3975,7 @@
         <v>-6.5</v>
       </c>
       <c r="D197">
-        <v>-0.5893836617469788</v>
+        <v>-0.4152162969112396</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -3989,7 +3989,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D198">
-        <v>2.297569513320923</v>
+        <v>2.902776956558228</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4003,7 +4003,7 @@
         <v>0</v>
       </c>
       <c r="D199">
-        <v>0.5756831169128418</v>
+        <v>0.1728328764438629</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4017,7 +4017,7 @@
         <v>-0.4000000059604645</v>
       </c>
       <c r="D200">
-        <v>0.08983516693115234</v>
+        <v>0.3269910216331482</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4031,7 +4031,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D201">
-        <v>0.3157260715961456</v>
+        <v>0.0556148886680603</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4045,7 +4045,7 @@
         <v>5.5</v>
       </c>
       <c r="D202">
-        <v>2.600017547607422</v>
+        <v>2.18379282951355</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4059,7 +4059,7 @@
         <v>-1.899999976158142</v>
       </c>
       <c r="D203">
-        <v>-1.358158111572266</v>
+        <v>-0.5658148527145386</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4073,7 +4073,7 @@
         <v>1.5</v>
       </c>
       <c r="D204">
-        <v>2.833492994308472</v>
+        <v>2.430994749069214</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4087,7 +4087,7 @@
         <v>-1.600000023841858</v>
       </c>
       <c r="D205">
-        <v>-3.229540824890137</v>
+        <v>-4.724509716033936</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4101,7 +4101,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D206">
-        <v>-0.2652164101600647</v>
+        <v>-0.2369660139083862</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4115,7 +4115,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D207">
-        <v>3.035766124725342</v>
+        <v>2.366576433181763</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4129,7 +4129,7 @@
         <v>1</v>
       </c>
       <c r="D208">
-        <v>0.8729122281074524</v>
+        <v>0.560664176940918</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4143,7 +4143,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D209">
-        <v>1.240222692489624</v>
+        <v>1.634517312049866</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4157,7 +4157,7 @@
         <v>-0.1000000014901161</v>
       </c>
       <c r="D210">
-        <v>0.3745561242103577</v>
+        <v>0.4067918062210083</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4171,7 +4171,7 @@
         <v>-2</v>
       </c>
       <c r="D211">
-        <v>1.795092582702637</v>
+        <v>1.701673746109009</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4185,7 +4185,7 @@
         <v>-9.699999809265137</v>
       </c>
       <c r="D212">
-        <v>-7.568035125732422</v>
+        <v>-6.96834659576416</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4199,7 +4199,7 @@
         <v>-2.700000047683716</v>
       </c>
       <c r="D213">
-        <v>-0.01688715815544128</v>
+        <v>-0.3001022636890411</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4213,7 +4213,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D214">
-        <v>2.692973375320435</v>
+        <v>2.027963876724243</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4227,7 +4227,7 @@
         <v>6.599999904632568</v>
       </c>
       <c r="D215">
-        <v>3.159879684448242</v>
+        <v>4.566423416137695</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4241,7 +4241,7 @@
         <v>-2.799999952316284</v>
       </c>
       <c r="D216">
-        <v>4.155763149261475</v>
+        <v>3.731854200363159</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4255,7 +4255,7 @@
         <v>9</v>
       </c>
       <c r="D217">
-        <v>3.915169954299927</v>
+        <v>6.192186832427979</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4269,7 +4269,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D218">
-        <v>4.013633728027344</v>
+        <v>3.982304573059082</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4283,7 +4283,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D219">
-        <v>2.992462635040283</v>
+        <v>3.386495590209961</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4297,7 +4297,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D220">
-        <v>-0.1589770913124084</v>
+        <v>-0.1417057514190674</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4311,7 +4311,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D221">
-        <v>0.7574585676193237</v>
+        <v>2.054567337036133</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4325,7 +4325,7 @@
         <v>-3.5</v>
       </c>
       <c r="D222">
-        <v>0.6694191098213196</v>
+        <v>0.4101301729679108</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4339,7 +4339,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D223">
-        <v>1.308875799179077</v>
+        <v>-0.1012546718120575</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4353,7 +4353,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D224">
-        <v>-2.243690729141235</v>
+        <v>-3.321291208267212</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4367,7 +4367,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D225">
-        <v>0.09130412340164185</v>
+        <v>0.1377671658992767</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4381,7 +4381,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D226">
-        <v>1.14295506477356</v>
+        <v>1.01885724067688</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -4395,7 +4395,7 @@
         <v>-3.5</v>
       </c>
       <c r="D227">
-        <v>-2.292304277420044</v>
+        <v>-0.9066534042358398</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -4409,7 +4409,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D228">
-        <v>-0.1917772889137268</v>
+        <v>-0.04010385274887085</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -4423,7 +4423,7 @@
         <v>-11</v>
       </c>
       <c r="D229">
-        <v>-7.180431365966797</v>
+        <v>-7.217569351196289</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -4437,7 +4437,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D230">
-        <v>2.97633171081543</v>
+        <v>3.572513103485107</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -4451,7 +4451,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D231">
-        <v>1.539173364639282</v>
+        <v>1.075824022293091</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -4465,7 +4465,7 @@
         <v>-6.699999809265137</v>
       </c>
       <c r="D232">
-        <v>-3.080196619033813</v>
+        <v>-2.120487213134766</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -4479,7 +4479,7 @@
         <v>-0.1000000014901161</v>
       </c>
       <c r="D233">
-        <v>0.9390957355499268</v>
+        <v>0.9846040010452271</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -4493,7 +4493,7 @@
         <v>-4.300000190734863</v>
       </c>
       <c r="D234">
-        <v>-3.05229115486145</v>
+        <v>-2.068907022476196</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -4507,7 +4507,7 @@
         <v>-0.5</v>
       </c>
       <c r="D235">
-        <v>2.061623811721802</v>
+        <v>0.7447298765182495</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -4521,7 +4521,7 @@
         <v>0</v>
       </c>
       <c r="D236">
-        <v>0.1656058430671692</v>
+        <v>-0.161080002784729</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -4535,7 +4535,7 @@
         <v>-0.5</v>
       </c>
       <c r="D237">
-        <v>-0.4518367648124695</v>
+        <v>-0.2022157311439514</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -4549,7 +4549,7 @@
         <v>-1.700000047683716</v>
       </c>
       <c r="D238">
-        <v>-0.9417992234230042</v>
+        <v>-0.8566733598709106</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -4563,7 +4563,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D239">
-        <v>3.292203187942505</v>
+        <v>3.662355661392212</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -4577,7 +4577,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D240">
-        <v>2.615202903747559</v>
+        <v>3.239773988723755</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -4591,7 +4591,7 @@
         <v>6.699999809265137</v>
       </c>
       <c r="D241">
-        <v>4.174993515014648</v>
+        <v>2.856295347213745</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -4605,7 +4605,7 @@
         <v>-3.799999952316284</v>
       </c>
       <c r="D242">
-        <v>-0.169257640838623</v>
+        <v>-0.344530314207077</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -4619,7 +4619,7 @@
         <v>3.5</v>
       </c>
       <c r="D243">
-        <v>1.271717548370361</v>
+        <v>0.9111635684967041</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -4633,7 +4633,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D244">
-        <v>2.651193380355835</v>
+        <v>2.639349460601807</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -4647,7 +4647,7 @@
         <v>2</v>
       </c>
       <c r="D245">
-        <v>-0.07353350520133972</v>
+        <v>0.3309500813484192</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -4661,7 +4661,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D246">
-        <v>0.8693849444389343</v>
+        <v>1.790052652359009</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -4675,7 +4675,7 @@
         <v>0</v>
       </c>
       <c r="D247">
-        <v>0.3183016180992126</v>
+        <v>0.02924098074436188</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -4689,7 +4689,7 @@
         <v>6.400000095367432</v>
       </c>
       <c r="D248">
-        <v>3.328604221343994</v>
+        <v>3.140321969985962</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -4703,7 +4703,7 @@
         <v>20.5</v>
       </c>
       <c r="D249">
-        <v>0.5770872831344604</v>
+        <v>0.09614884853363037</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -4717,7 +4717,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D250">
-        <v>-2.268792629241943</v>
+        <v>2.816663980484009</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -4731,7 +4731,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D251">
-        <v>1.731877565383911</v>
+        <v>1.700815439224243</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -4745,7 +4745,7 @@
         <v>-1.700000047683716</v>
       </c>
       <c r="D252">
-        <v>0.4240583181381226</v>
+        <v>0.1034674793481827</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -4759,7 +4759,7 @@
         <v>1</v>
       </c>
       <c r="D253">
-        <v>2.466982126235962</v>
+        <v>1.87914514541626</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -4773,7 +4773,7 @@
         <v>1</v>
       </c>
       <c r="D254">
-        <v>0.08583450317382812</v>
+        <v>0.8199698925018311</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -4787,7 +4787,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D255">
-        <v>2.940244436264038</v>
+        <v>1.820298194885254</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -4801,7 +4801,7 @@
         <v>11.39999961853027</v>
       </c>
       <c r="D256">
-        <v>3.54755687713623</v>
+        <v>5.075541496276855</v>
       </c>
     </row>
     <row r="257" spans="1:4">
@@ -4815,7 +4815,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D257">
-        <v>3.960403680801392</v>
+        <v>2.978990316390991</v>
       </c>
     </row>
     <row r="258" spans="1:4">
@@ -4829,7 +4829,7 @@
         <v>10.5</v>
       </c>
       <c r="D258">
-        <v>2.843266248703003</v>
+        <v>2.545902729034424</v>
       </c>
     </row>
     <row r="259" spans="1:4">
@@ -4843,7 +4843,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D259">
-        <v>2.760072946548462</v>
+        <v>2.694518327713013</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -4857,7 +4857,7 @@
         <v>1.5</v>
       </c>
       <c r="D260">
-        <v>-0.05749398469924927</v>
+        <v>0.05763208866119385</v>
       </c>
     </row>
     <row r="261" spans="1:4">
@@ -4871,7 +4871,7 @@
         <v>0.5</v>
       </c>
       <c r="D261">
-        <v>1.130005836486816</v>
+        <v>0.7579983472824097</v>
       </c>
     </row>
     <row r="262" spans="1:4">
@@ -4885,7 +4885,7 @@
         <v>-3.099999904632568</v>
       </c>
       <c r="D262">
-        <v>0.9243768453598022</v>
+        <v>0.8268610239028931</v>
       </c>
     </row>
     <row r="263" spans="1:4">
@@ -4899,7 +4899,7 @@
         <v>-1.600000023841858</v>
       </c>
       <c r="D263">
-        <v>-2.178890466690063</v>
+        <v>-1.4072585105896</v>
       </c>
     </row>
     <row r="264" spans="1:4">
@@ -4913,7 +4913,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D264">
-        <v>1.08667266368866</v>
+        <v>1.090427875518799</v>
       </c>
     </row>
     <row r="265" spans="1:4">
@@ -4927,7 +4927,7 @@
         <v>8.399999618530273</v>
       </c>
       <c r="D265">
-        <v>2.274670839309692</v>
+        <v>1.522443771362305</v>
       </c>
     </row>
     <row r="266" spans="1:4">
@@ -4941,7 +4941,7 @@
         <v>-0.6000000238418579</v>
       </c>
       <c r="D266">
-        <v>-0.2952249646186829</v>
+        <v>-0.1263147592544556</v>
       </c>
     </row>
     <row r="267" spans="1:4">
@@ -4955,7 +4955,7 @@
         <v>-4.599999904632568</v>
       </c>
       <c r="D267">
-        <v>1.469467163085938</v>
+        <v>2.546689033508301</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -4969,7 +4969,7 @@
         <v>5.400000095367432</v>
       </c>
       <c r="D268">
-        <v>1.687505722045898</v>
+        <v>2.54136061668396</v>
       </c>
     </row>
     <row r="269" spans="1:4">
@@ -4983,7 +4983,7 @@
         <v>7.599999904632568</v>
       </c>
       <c r="D269">
-        <v>7.346232414245605</v>
+        <v>8.301024436950684</v>
       </c>
     </row>
     <row r="270" spans="1:4">
@@ -4997,7 +4997,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D270">
-        <v>0.04241174459457397</v>
+        <v>0.03343302011489868</v>
       </c>
     </row>
     <row r="271" spans="1:4">
@@ -5011,7 +5011,7 @@
         <v>-2.5</v>
       </c>
       <c r="D271">
-        <v>0.08471554517745972</v>
+        <v>0.1601720452308655</v>
       </c>
     </row>
     <row r="272" spans="1:4">
@@ -5025,7 +5025,7 @@
         <v>-2.400000095367432</v>
       </c>
       <c r="D272">
-        <v>0.189044788479805</v>
+        <v>0.2160468846559525</v>
       </c>
     </row>
     <row r="273" spans="1:4">
@@ -5039,7 +5039,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D273">
-        <v>-1.268617868423462</v>
+        <v>-2.906922101974487</v>
       </c>
     </row>
     <row r="274" spans="1:4">
@@ -5053,7 +5053,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D274">
-        <v>0.2654979228973389</v>
+        <v>0.1949471533298492</v>
       </c>
     </row>
     <row r="275" spans="1:4">
@@ -5067,7 +5067,7 @@
         <v>-1.700000047683716</v>
       </c>
       <c r="D275">
-        <v>-0.6857908368110657</v>
+        <v>-0.1451005637645721</v>
       </c>
     </row>
     <row r="276" spans="1:4">
@@ -5081,7 +5081,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D276">
-        <v>0.5296509861946106</v>
+        <v>0.2424907833337784</v>
       </c>
     </row>
     <row r="277" spans="1:4">
@@ -5095,7 +5095,7 @@
         <v>-1.399999976158142</v>
       </c>
       <c r="D277">
-        <v>0.8871288299560547</v>
+        <v>1.004608988761902</v>
       </c>
     </row>
     <row r="278" spans="1:4">
@@ -5109,7 +5109,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D278">
-        <v>1.369930267333984</v>
+        <v>0.7367472648620605</v>
       </c>
     </row>
     <row r="279" spans="1:4">
@@ -5123,7 +5123,7 @@
         <v>-1.299999952316284</v>
       </c>
       <c r="D279">
-        <v>0.02974402904510498</v>
+        <v>-0.1488119065761566</v>
       </c>
     </row>
     <row r="280" spans="1:4">
@@ -5137,7 +5137,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D280">
-        <v>0.4853165745735168</v>
+        <v>0.3510761559009552</v>
       </c>
     </row>
     <row r="281" spans="1:4">
@@ -5151,7 +5151,7 @@
         <v>-2.299999952316284</v>
       </c>
       <c r="D281">
-        <v>0.6211867332458496</v>
+        <v>-0.03615891933441162</v>
       </c>
     </row>
     <row r="282" spans="1:4">
@@ -5165,7 +5165,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D282">
-        <v>-0.8249276280403137</v>
+        <v>-0.4239958822727203</v>
       </c>
     </row>
     <row r="283" spans="1:4">
@@ -5179,7 +5179,7 @@
         <v>5.300000190734863</v>
       </c>
       <c r="D283">
-        <v>2.989335298538208</v>
+        <v>3.494840860366821</v>
       </c>
     </row>
     <row r="284" spans="1:4">
@@ -5193,7 +5193,7 @@
         <v>-1.399999976158142</v>
       </c>
       <c r="D284">
-        <v>1.84475040435791</v>
+        <v>1.602497816085815</v>
       </c>
     </row>
     <row r="285" spans="1:4">
@@ -5207,7 +5207,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D285">
-        <v>0.8939393162727356</v>
+        <v>0.8112000226974487</v>
       </c>
     </row>
     <row r="286" spans="1:4">
@@ -5221,7 +5221,7 @@
         <v>2.5</v>
       </c>
       <c r="D286">
-        <v>-2.814810037612915</v>
+        <v>-2.499597549438477</v>
       </c>
     </row>
     <row r="287" spans="1:4">
@@ -5235,7 +5235,7 @@
         <v>1</v>
       </c>
       <c r="D287">
-        <v>0.6809408664703369</v>
+        <v>0.6324225068092346</v>
       </c>
     </row>
     <row r="288" spans="1:4">
@@ -5249,7 +5249,7 @@
         <v>-4.199999809265137</v>
       </c>
       <c r="D288">
-        <v>0.3112619519233704</v>
+        <v>0.05556905269622803</v>
       </c>
     </row>
     <row r="289" spans="1:4">
@@ -5263,7 +5263,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D289">
-        <v>2.183435916900635</v>
+        <v>0.3782267868518829</v>
       </c>
     </row>
     <row r="290" spans="1:4">
@@ -5277,7 +5277,7 @@
         <v>0</v>
       </c>
       <c r="D290">
-        <v>0.4356071352958679</v>
+        <v>-0.1595298945903778</v>
       </c>
     </row>
     <row r="291" spans="1:4">
@@ -5291,7 +5291,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D291">
-        <v>-0.2328581809997559</v>
+        <v>-0.4225509464740753</v>
       </c>
     </row>
     <row r="292" spans="1:4">
@@ -5305,7 +5305,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D292">
-        <v>-0.001006245613098145</v>
+        <v>0.06142222881317139</v>
       </c>
     </row>
     <row r="293" spans="1:4">
@@ -5319,7 +5319,7 @@
         <v>-13.5</v>
       </c>
       <c r="D293">
-        <v>-4.699225425720215</v>
+        <v>-5.49592399597168</v>
       </c>
     </row>
     <row r="294" spans="1:4">
@@ -5333,7 +5333,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D294">
-        <v>2.869349002838135</v>
+        <v>2.136647701263428</v>
       </c>
     </row>
     <row r="295" spans="1:4">
@@ -5347,7 +5347,7 @@
         <v>13.30000019073486</v>
       </c>
       <c r="D295">
-        <v>5.440198421478271</v>
+        <v>7.428242206573486</v>
       </c>
     </row>
     <row r="296" spans="1:4">
@@ -5361,7 +5361,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D296">
-        <v>-0.7204590439796448</v>
+        <v>-0.3737469017505646</v>
       </c>
     </row>
     <row r="297" spans="1:4">
@@ -5375,7 +5375,7 @@
         <v>5</v>
       </c>
       <c r="D297">
-        <v>1.462313175201416</v>
+        <v>1.586734175682068</v>
       </c>
     </row>
     <row r="298" spans="1:4">
@@ -5389,7 +5389,7 @@
         <v>-2.299999952316284</v>
       </c>
       <c r="D298">
-        <v>0.01725068688392639</v>
+        <v>0.3276387453079224</v>
       </c>
     </row>
     <row r="299" spans="1:4">
@@ -5403,7 +5403,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D299">
-        <v>0.4523048102855682</v>
+        <v>1.21487557888031</v>
       </c>
     </row>
     <row r="300" spans="1:4">
@@ -5417,7 +5417,7 @@
         <v>8.399999618530273</v>
       </c>
       <c r="D300">
-        <v>2.225934743881226</v>
+        <v>2.734039068222046</v>
       </c>
     </row>
     <row r="301" spans="1:4">
@@ -5431,7 +5431,7 @@
         <v>-8</v>
       </c>
       <c r="D301">
-        <v>-7.524496078491211</v>
+        <v>-8.080245971679688</v>
       </c>
     </row>
     <row r="302" spans="1:4">
@@ -5445,7 +5445,7 @@
         <v>0.5</v>
       </c>
       <c r="D302">
-        <v>3.490952491760254</v>
+        <v>3.360867977142334</v>
       </c>
     </row>
     <row r="303" spans="1:4">
@@ -5459,7 +5459,7 @@
         <v>-1.100000023841858</v>
       </c>
       <c r="D303">
-        <v>1.240955352783203</v>
+        <v>-0.1379827558994293</v>
       </c>
     </row>
     <row r="304" spans="1:4">
@@ -5473,7 +5473,7 @@
         <v>-1.100000023841858</v>
       </c>
       <c r="D304">
-        <v>-0.09363770484924316</v>
+        <v>-0.2533573508262634</v>
       </c>
     </row>
     <row r="305" spans="1:4">
@@ -5487,7 +5487,7 @@
         <v>3</v>
       </c>
       <c r="D305">
-        <v>2.333333015441895</v>
+        <v>1.839389324188232</v>
       </c>
     </row>
     <row r="306" spans="1:4">
@@ -5501,7 +5501,7 @@
         <v>5</v>
       </c>
       <c r="D306">
-        <v>0.3905006647109985</v>
+        <v>0.001518160104751587</v>
       </c>
     </row>
     <row r="307" spans="1:4">
@@ -5515,7 +5515,7 @@
         <v>-8.899999618530273</v>
       </c>
       <c r="D307">
-        <v>-4.006278038024902</v>
+        <v>-4.049857616424561</v>
       </c>
     </row>
     <row r="308" spans="1:4">
@@ -5529,7 +5529,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D308">
-        <v>0.8869526982307434</v>
+        <v>-0.007856518030166626</v>
       </c>
     </row>
     <row r="309" spans="1:4">
@@ -5543,7 +5543,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D309">
-        <v>3.029425382614136</v>
+        <v>2.419414758682251</v>
       </c>
     </row>
     <row r="310" spans="1:4">
@@ -5557,7 +5557,7 @@
         <v>1.5</v>
       </c>
       <c r="D310">
-        <v>0.8011590242385864</v>
+        <v>0.7027767896652222</v>
       </c>
     </row>
     <row r="311" spans="1:4">
@@ -5571,7 +5571,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D311">
-        <v>-0.3705339431762695</v>
+        <v>0.2572997808456421</v>
       </c>
     </row>
     <row r="312" spans="1:4">
@@ -5585,7 +5585,7 @@
         <v>-0.5</v>
       </c>
       <c r="D312">
-        <v>0.134692370891571</v>
+        <v>0.08085943758487701</v>
       </c>
     </row>
     <row r="313" spans="1:4">
@@ -5599,7 +5599,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D313">
-        <v>-0.4369595050811768</v>
+        <v>-0.09224984049797058</v>
       </c>
     </row>
     <row r="314" spans="1:4">
@@ -5613,7 +5613,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D314">
-        <v>0.4118880033493042</v>
+        <v>0.2307391315698624</v>
       </c>
     </row>
     <row r="315" spans="1:4">
@@ -5627,7 +5627,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D315">
-        <v>0.5703698396682739</v>
+        <v>-0.1349242627620697</v>
       </c>
     </row>
     <row r="316" spans="1:4">
@@ -5641,7 +5641,7 @@
         <v>-0.1000000014901161</v>
       </c>
       <c r="D316">
-        <v>-0.1700227856636047</v>
+        <v>0.2323693931102753</v>
       </c>
     </row>
     <row r="317" spans="1:4">
@@ -5655,7 +5655,7 @@
         <v>6.599999904632568</v>
       </c>
       <c r="D317">
-        <v>4.655464172363281</v>
+        <v>5.434839248657227</v>
       </c>
     </row>
     <row r="318" spans="1:4">
@@ -5669,7 +5669,7 @@
         <v>-0.2000000029802322</v>
       </c>
       <c r="D318">
-        <v>3.653324842453003</v>
+        <v>3.783581018447876</v>
       </c>
     </row>
     <row r="319" spans="1:4">
@@ -5683,7 +5683,7 @@
         <v>-2.099999904632568</v>
       </c>
       <c r="D319">
-        <v>1.78973650932312</v>
+        <v>1.218987464904785</v>
       </c>
     </row>
     <row r="320" spans="1:4">
@@ -5697,7 +5697,7 @@
         <v>4</v>
       </c>
       <c r="D320">
-        <v>-0.179767906665802</v>
+        <v>0.06792409718036652</v>
       </c>
     </row>
     <row r="321" spans="1:4">
@@ -5711,7 +5711,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D321">
-        <v>1.135438442230225</v>
+        <v>1.211090087890625</v>
       </c>
     </row>
     <row r="322" spans="1:4">
@@ -5725,7 +5725,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D322">
-        <v>2.206586122512817</v>
+        <v>1.688512802124023</v>
       </c>
     </row>
     <row r="323" spans="1:4">
@@ -5739,7 +5739,7 @@
         <v>7.199999809265137</v>
       </c>
       <c r="D323">
-        <v>1.729410886764526</v>
+        <v>0.8509528636932373</v>
       </c>
     </row>
     <row r="324" spans="1:4">
@@ -5753,7 +5753,7 @@
         <v>2</v>
       </c>
       <c r="D324">
-        <v>0.9513276219367981</v>
+        <v>2.3554527759552</v>
       </c>
     </row>
     <row r="325" spans="1:4">
@@ -5767,7 +5767,7 @@
         <v>-0.6000000238418579</v>
       </c>
       <c r="D325">
-        <v>-0.3393254280090332</v>
+        <v>0.09121903777122498</v>
       </c>
     </row>
     <row r="326" spans="1:4">
@@ -5781,7 +5781,7 @@
         <v>-6</v>
       </c>
       <c r="D326">
-        <v>-4.879124641418457</v>
+        <v>-3.785841703414917</v>
       </c>
     </row>
     <row r="327" spans="1:4">
@@ -5795,7 +5795,7 @@
         <v>1.5</v>
       </c>
       <c r="D327">
-        <v>0.8650870323181152</v>
+        <v>0.6258977055549622</v>
       </c>
     </row>
     <row r="328" spans="1:4">
@@ -5809,7 +5809,7 @@
         <v>3.5</v>
       </c>
       <c r="D328">
-        <v>3.70693564414978</v>
+        <v>3.637876510620117</v>
       </c>
     </row>
     <row r="329" spans="1:4">
@@ -5823,7 +5823,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D329">
-        <v>1.680596590042114</v>
+        <v>2.83531928062439</v>
       </c>
     </row>
     <row r="330" spans="1:4">
@@ -5837,7 +5837,7 @@
         <v>-1.799999952316284</v>
       </c>
       <c r="D330">
-        <v>-0.04649704694747925</v>
+        <v>-0.1573047339916229</v>
       </c>
     </row>
     <row r="331" spans="1:4">
@@ -5851,7 +5851,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D331">
-        <v>-2.865114450454712</v>
+        <v>-2.435778379440308</v>
       </c>
     </row>
     <row r="332" spans="1:4">
@@ -5865,7 +5865,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D332">
-        <v>0.4202933609485626</v>
+        <v>0.9627169370651245</v>
       </c>
     </row>
     <row r="333" spans="1:4">
@@ -5879,7 +5879,7 @@
         <v>-0.4000000059604645</v>
       </c>
       <c r="D333">
-        <v>-0.1422286629676819</v>
+        <v>-0.1226613819599152</v>
       </c>
     </row>
     <row r="334" spans="1:4">
@@ -5893,7 +5893,7 @@
         <v>7.5</v>
       </c>
       <c r="D334">
-        <v>4.565656661987305</v>
+        <v>4.964570999145508</v>
       </c>
     </row>
     <row r="335" spans="1:4">
@@ -5907,7 +5907,7 @@
         <v>-0.8999999761581421</v>
       </c>
       <c r="D335">
-        <v>0.1943424046039581</v>
+        <v>0.1236400157213211</v>
       </c>
     </row>
     <row r="336" spans="1:4">
@@ -5921,7 +5921,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D336">
-        <v>0.9852912425994873</v>
+        <v>0.05191595852375031</v>
       </c>
     </row>
     <row r="337" spans="1:4">
@@ -5935,7 +5935,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D337">
-        <v>0.4827447533607483</v>
+        <v>0.481738418340683</v>
       </c>
     </row>
     <row r="338" spans="1:4">
@@ -5949,7 +5949,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D338">
-        <v>0.3884175717830658</v>
+        <v>1.690019488334656</v>
       </c>
     </row>
     <row r="339" spans="1:4">
@@ -5963,7 +5963,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D339">
-        <v>0.07623383402824402</v>
+        <v>0.5337027907371521</v>
       </c>
     </row>
     <row r="340" spans="1:4">
@@ -5977,7 +5977,7 @@
         <v>-6.900000095367432</v>
       </c>
       <c r="D340">
-        <v>-5.529664516448975</v>
+        <v>-3.828852415084839</v>
       </c>
     </row>
     <row r="341" spans="1:4">
@@ -5991,7 +5991,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D341">
-        <v>0.5163209438323975</v>
+        <v>0.5795602798461914</v>
       </c>
     </row>
     <row r="342" spans="1:4">
@@ -6005,7 +6005,7 @@
         <v>-0.2000000029802322</v>
       </c>
       <c r="D342">
-        <v>-0.06828063726425171</v>
+        <v>-0.2112520337104797</v>
       </c>
     </row>
     <row r="343" spans="1:4">
@@ -6019,7 +6019,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D343">
-        <v>-0.3568339943885803</v>
+        <v>-0.1749015748500824</v>
       </c>
     </row>
     <row r="344" spans="1:4">
@@ -6033,7 +6033,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D344">
-        <v>-0.8082218766212463</v>
+        <v>-0.3240839540958405</v>
       </c>
     </row>
     <row r="345" spans="1:4">
@@ -6047,7 +6047,7 @@
         <v>-0.2000000029802322</v>
       </c>
       <c r="D345">
-        <v>0.9230043292045593</v>
+        <v>0.9960606098175049</v>
       </c>
     </row>
     <row r="346" spans="1:4">
@@ -6061,7 +6061,7 @@
         <v>-0.300000011920929</v>
       </c>
       <c r="D346">
-        <v>-0.1144415736198425</v>
+        <v>-0.1944993734359741</v>
       </c>
     </row>
     <row r="347" spans="1:4">
@@ -6075,7 +6075,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D347">
-        <v>4.385956287384033</v>
+        <v>4.337251663208008</v>
       </c>
     </row>
     <row r="348" spans="1:4">
@@ -6089,7 +6089,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D348">
-        <v>2.992654085159302</v>
+        <v>2.256336212158203</v>
       </c>
     </row>
     <row r="349" spans="1:4">
@@ -6103,7 +6103,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D349">
-        <v>2.193653345108032</v>
+        <v>2.23436713218689</v>
       </c>
     </row>
     <row r="350" spans="1:4">
@@ -6117,7 +6117,7 @@
         <v>4</v>
       </c>
       <c r="D350">
-        <v>2.694771528244019</v>
+        <v>2.204325914382935</v>
       </c>
     </row>
     <row r="351" spans="1:4">
@@ -6131,7 +6131,7 @@
         <v>-1.600000023841858</v>
       </c>
       <c r="D351">
-        <v>0.9865489602088928</v>
+        <v>0.1042084693908691</v>
       </c>
     </row>
     <row r="352" spans="1:4">
@@ -6145,7 +6145,7 @@
         <v>-3</v>
       </c>
       <c r="D352">
-        <v>-0.9248676896095276</v>
+        <v>-0.653275728225708</v>
       </c>
     </row>
     <row r="353" spans="1:4">
@@ -6159,7 +6159,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D353">
-        <v>1.642061471939087</v>
+        <v>1.778199791908264</v>
       </c>
     </row>
     <row r="354" spans="1:4">
@@ -6173,7 +6173,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D354">
-        <v>0.365379810333252</v>
+        <v>0.09494656324386597</v>
       </c>
     </row>
     <row r="355" spans="1:4">
@@ -6187,7 +6187,7 @@
         <v>4</v>
       </c>
       <c r="D355">
-        <v>2.780240774154663</v>
+        <v>3.279483079910278</v>
       </c>
     </row>
     <row r="356" spans="1:4">
@@ -6201,7 +6201,7 @@
         <v>9.399999618530273</v>
       </c>
       <c r="D356">
-        <v>5.204900741577148</v>
+        <v>4.531404495239258</v>
       </c>
     </row>
     <row r="357" spans="1:4">
@@ -6215,7 +6215,7 @@
         <v>5.300000190734863</v>
       </c>
       <c r="D357">
-        <v>5.865140438079834</v>
+        <v>5.976909637451172</v>
       </c>
     </row>
     <row r="358" spans="1:4">
@@ -6229,7 +6229,7 @@
         <v>-0.1000000014901161</v>
       </c>
       <c r="D358">
-        <v>1.025132656097412</v>
+        <v>0.8299412727355957</v>
       </c>
     </row>
     <row r="359" spans="1:4">
@@ -6243,7 +6243,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D359">
-        <v>1.711039066314697</v>
+        <v>0.6704239845275879</v>
       </c>
     </row>
     <row r="360" spans="1:4">
@@ -6257,7 +6257,7 @@
         <v>-1.799999952316284</v>
       </c>
       <c r="D360">
-        <v>-0.3974673748016357</v>
+        <v>-0.4002564251422882</v>
       </c>
     </row>
     <row r="361" spans="1:4">
@@ -6271,7 +6271,7 @@
         <v>4.5</v>
       </c>
       <c r="D361">
-        <v>1.470196008682251</v>
+        <v>1.562188744544983</v>
       </c>
     </row>
     <row r="362" spans="1:4">
@@ -6285,7 +6285,7 @@
         <v>-2.5</v>
       </c>
       <c r="D362">
-        <v>0.2323005795478821</v>
+        <v>0.09578385204076767</v>
       </c>
     </row>
     <row r="363" spans="1:4">
@@ -6299,7 +6299,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D363">
-        <v>2.855592012405396</v>
+        <v>3.032263994216919</v>
       </c>
     </row>
     <row r="364" spans="1:4">
@@ -6313,7 +6313,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D364">
-        <v>0.333287239074707</v>
+        <v>-0.6026705503463745</v>
       </c>
     </row>
     <row r="365" spans="1:4">
@@ -6327,7 +6327,7 @@
         <v>-12.89999961853027</v>
       </c>
       <c r="D365">
-        <v>-3.72647500038147</v>
+        <v>-3.502775192260742</v>
       </c>
     </row>
     <row r="366" spans="1:4">
@@ -6341,7 +6341,7 @@
         <v>2.5</v>
       </c>
       <c r="D366">
-        <v>1.810633897781372</v>
+        <v>1.924805164337158</v>
       </c>
     </row>
     <row r="367" spans="1:4">
@@ -6355,7 +6355,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D367">
-        <v>0.8011736869812012</v>
+        <v>0.3125708699226379</v>
       </c>
     </row>
     <row r="368" spans="1:4">
@@ -6369,7 +6369,7 @@
         <v>11.69999980926514</v>
       </c>
       <c r="D368">
-        <v>5.428711891174316</v>
+        <v>4.461206436157227</v>
       </c>
     </row>
     <row r="369" spans="1:4">
@@ -6383,7 +6383,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D369">
-        <v>0.1196751594543457</v>
+        <v>-0.02586871385574341</v>
       </c>
     </row>
     <row r="370" spans="1:4">
@@ -6397,7 +6397,7 @@
         <v>-9.100000381469727</v>
       </c>
       <c r="D370">
-        <v>-6.273085117340088</v>
+        <v>-7.689004898071289</v>
       </c>
     </row>
     <row r="371" spans="1:4">
@@ -6411,7 +6411,7 @@
         <v>3.5</v>
       </c>
       <c r="D371">
-        <v>4.381670951843262</v>
+        <v>3.82455039024353</v>
       </c>
     </row>
     <row r="372" spans="1:4">
@@ -6425,7 +6425,7 @@
         <v>0.5</v>
       </c>
       <c r="D372">
-        <v>0.9483404755592346</v>
+        <v>0.5676824450492859</v>
       </c>
     </row>
     <row r="373" spans="1:4">
@@ -6439,7 +6439,7 @@
         <v>-2.900000095367432</v>
       </c>
       <c r="D373">
-        <v>-2.594305753707886</v>
+        <v>-2.265953302383423</v>
       </c>
     </row>
     <row r="374" spans="1:4">
@@ -6453,7 +6453,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D374">
-        <v>0.6668245792388916</v>
+        <v>0.2408526390790939</v>
       </c>
     </row>
     <row r="375" spans="1:4">
@@ -6467,7 +6467,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D375">
-        <v>2.590429544448853</v>
+        <v>2.369516134262085</v>
       </c>
     </row>
     <row r="376" spans="1:4">
@@ -6481,7 +6481,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D376">
-        <v>1.036961317062378</v>
+        <v>1.195230603218079</v>
       </c>
     </row>
     <row r="377" spans="1:4">
@@ -6495,7 +6495,7 @@
         <v>-0.1000000014901161</v>
       </c>
       <c r="D377">
-        <v>0.657223641872406</v>
+        <v>0.1598879992961884</v>
       </c>
     </row>
     <row r="378" spans="1:4">
@@ -6509,7 +6509,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D378">
-        <v>2.876779794692993</v>
+        <v>2.970301389694214</v>
       </c>
     </row>
     <row r="379" spans="1:4">
@@ -6523,7 +6523,7 @@
         <v>-4.800000190734863</v>
       </c>
       <c r="D379">
-        <v>-1.753895998001099</v>
+        <v>-2.228427886962891</v>
       </c>
     </row>
     <row r="380" spans="1:4">
@@ -6537,7 +6537,7 @@
         <v>-1.200000047683716</v>
       </c>
       <c r="D380">
-        <v>0.04041552543640137</v>
+        <v>-0.05471304059028625</v>
       </c>
     </row>
     <row r="381" spans="1:4">
@@ -6551,7 +6551,7 @@
         <v>-2</v>
       </c>
       <c r="D381">
-        <v>-0.4922746419906616</v>
+        <v>0.1517774909734726</v>
       </c>
     </row>
     <row r="382" spans="1:4">
@@ -6565,7 +6565,7 @@
         <v>-3.799999952316284</v>
       </c>
       <c r="D382">
-        <v>-2.914268732070923</v>
+        <v>-2.3984534740448</v>
       </c>
     </row>
     <row r="383" spans="1:4">
@@ -6579,7 +6579,7 @@
         <v>-1.600000023841858</v>
       </c>
       <c r="D383">
-        <v>-0.3616797924041748</v>
+        <v>-0.4737388789653778</v>
       </c>
     </row>
     <row r="384" spans="1:4">
@@ -6593,7 +6593,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D384">
-        <v>-1.140535593032837</v>
+        <v>-0.4585865437984467</v>
       </c>
     </row>
     <row r="385" spans="1:4">
@@ -6607,7 +6607,7 @@
         <v>3.5</v>
       </c>
       <c r="D385">
-        <v>1.679963350296021</v>
+        <v>1.651585817337036</v>
       </c>
     </row>
     <row r="386" spans="1:4">
@@ -6621,7 +6621,7 @@
         <v>-0.4000000059604645</v>
       </c>
       <c r="D386">
-        <v>1.766678094863892</v>
+        <v>1.783711075782776</v>
       </c>
     </row>
     <row r="387" spans="1:4">
@@ -6635,7 +6635,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D387">
-        <v>2.691413640975952</v>
+        <v>3.436078786849976</v>
       </c>
     </row>
     <row r="388" spans="1:4">
@@ -6649,7 +6649,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D388">
-        <v>0.2086600661277771</v>
+        <v>0.132920041680336</v>
       </c>
     </row>
     <row r="389" spans="1:4">
@@ -6663,7 +6663,7 @@
         <v>-1.200000047683716</v>
       </c>
       <c r="D389">
-        <v>-0.098955899477005</v>
+        <v>0.08672869205474854</v>
       </c>
     </row>
     <row r="390" spans="1:4">
@@ -6677,7 +6677,7 @@
         <v>2.5</v>
       </c>
       <c r="D390">
-        <v>0.2711294293403625</v>
+        <v>-0.02692291140556335</v>
       </c>
     </row>
     <row r="391" spans="1:4">
@@ -6691,7 +6691,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D391">
-        <v>0.2995879948139191</v>
+        <v>0.6687439680099487</v>
       </c>
     </row>
     <row r="392" spans="1:4">
@@ -6705,7 +6705,7 @@
         <v>-1.5</v>
       </c>
       <c r="D392">
-        <v>-0.4425667524337769</v>
+        <v>0.3527809977531433</v>
       </c>
     </row>
     <row r="393" spans="1:4">
@@ -6719,7 +6719,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D393">
-        <v>0.1372696906328201</v>
+        <v>-0.2979622781276703</v>
       </c>
     </row>
     <row r="394" spans="1:4">
@@ -6733,7 +6733,7 @@
         <v>-0.1000000014901161</v>
       </c>
       <c r="D394">
-        <v>0.1277664303779602</v>
+        <v>0.1883185654878616</v>
       </c>
     </row>
     <row r="395" spans="1:4">
@@ -6747,7 +6747,7 @@
         <v>-1.5</v>
       </c>
       <c r="D395">
-        <v>-0.5507407784461975</v>
+        <v>0.6197736263275146</v>
       </c>
     </row>
     <row r="396" spans="1:4">
@@ -6761,7 +6761,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D396">
-        <v>1.432507276535034</v>
+        <v>1.176706671714783</v>
       </c>
     </row>
     <row r="397" spans="1:4">
@@ -6775,7 +6775,7 @@
         <v>-6.099999904632568</v>
       </c>
       <c r="D397">
-        <v>1.400202989578247</v>
+        <v>1.684658288955688</v>
       </c>
     </row>
     <row r="398" spans="1:4">
@@ -6789,7 +6789,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D398">
-        <v>2.988070249557495</v>
+        <v>3.215263605117798</v>
       </c>
     </row>
     <row r="399" spans="1:4">
@@ -6803,7 +6803,7 @@
         <v>1</v>
       </c>
       <c r="D399">
-        <v>0.6368485689163208</v>
+        <v>0.2936204373836517</v>
       </c>
     </row>
     <row r="400" spans="1:4">
@@ -6817,7 +6817,7 @@
         <v>6.400000095367432</v>
       </c>
       <c r="D400">
-        <v>3.794247150421143</v>
+        <v>4.311507701873779</v>
       </c>
     </row>
     <row r="401" spans="1:4">
@@ -6831,7 +6831,7 @@
         <v>4</v>
       </c>
       <c r="D401">
-        <v>1.758498668670654</v>
+        <v>1.610530138015747</v>
       </c>
     </row>
     <row r="402" spans="1:4">
@@ -6845,7 +6845,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D402">
-        <v>0.7056717872619629</v>
+        <v>0.3959847092628479</v>
       </c>
     </row>
     <row r="403" spans="1:4">
@@ -6859,7 +6859,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D403">
-        <v>0.9606370329856873</v>
+        <v>1.238598823547363</v>
       </c>
     </row>
     <row r="404" spans="1:4">
@@ -6873,7 +6873,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D404">
-        <v>0.5046393275260925</v>
+        <v>0.1000604629516602</v>
       </c>
     </row>
     <row r="405" spans="1:4">
@@ -6887,7 +6887,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D405">
-        <v>0.3310165405273438</v>
+        <v>0.4214771091938019</v>
       </c>
     </row>
     <row r="406" spans="1:4">
@@ -6901,7 +6901,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D406">
-        <v>1.801276683807373</v>
+        <v>2.056874990463257</v>
       </c>
     </row>
     <row r="407" spans="1:4">
@@ -6915,7 +6915,7 @@
         <v>-1.299999952316284</v>
       </c>
       <c r="D407">
-        <v>1.185089826583862</v>
+        <v>1.529510736465454</v>
       </c>
     </row>
     <row r="408" spans="1:4">
@@ -6929,7 +6929,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D408">
-        <v>2.258054971694946</v>
+        <v>1.796063780784607</v>
       </c>
     </row>
     <row r="409" spans="1:4">
@@ -6943,7 +6943,7 @@
         <v>4.5</v>
       </c>
       <c r="D409">
-        <v>0.6883870959281921</v>
+        <v>1.237138032913208</v>
       </c>
     </row>
     <row r="410" spans="1:4">
@@ -6957,7 +6957,7 @@
         <v>-4.199999809265137</v>
       </c>
       <c r="D410">
-        <v>0.4017661213874817</v>
+        <v>0.2959380745887756</v>
       </c>
     </row>
     <row r="411" spans="1:4">
@@ -6971,7 +6971,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D411">
-        <v>-0.8790492415428162</v>
+        <v>-0.3871141970157623</v>
       </c>
     </row>
     <row r="412" spans="1:4">
@@ -6985,7 +6985,7 @@
         <v>6.5</v>
       </c>
       <c r="D412">
-        <v>3.693346500396729</v>
+        <v>3.396953582763672</v>
       </c>
     </row>
     <row r="413" spans="1:4">
@@ -6999,7 +6999,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D413">
-        <v>3.335331201553345</v>
+        <v>1.670110464096069</v>
       </c>
     </row>
     <row r="414" spans="1:4">
@@ -7013,7 +7013,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D414">
-        <v>1.175100803375244</v>
+        <v>2.564220190048218</v>
       </c>
     </row>
     <row r="415" spans="1:4">
@@ -7027,7 +7027,7 @@
         <v>-3.5</v>
       </c>
       <c r="D415">
-        <v>-1.045067310333252</v>
+        <v>-1.223504662513733</v>
       </c>
     </row>
     <row r="416" spans="1:4">
@@ -7041,7 +7041,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D416">
-        <v>4.685215473175049</v>
+        <v>5.070016384124756</v>
       </c>
     </row>
     <row r="417" spans="1:4">
@@ -7055,7 +7055,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D417">
-        <v>3.617990255355835</v>
+        <v>2.556095361709595</v>
       </c>
     </row>
     <row r="418" spans="1:4">
@@ -7069,7 +7069,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D418">
-        <v>-1.014527797698975</v>
+        <v>-0.5427517890930176</v>
       </c>
     </row>
     <row r="419" spans="1:4">
@@ -7083,7 +7083,7 @@
         <v>-0.1000000014901161</v>
       </c>
       <c r="D419">
-        <v>0.2646249234676361</v>
+        <v>0.04142901301383972</v>
       </c>
     </row>
     <row r="420" spans="1:4">
@@ -7097,7 +7097,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D420">
-        <v>1.411293268203735</v>
+        <v>1.687508821487427</v>
       </c>
     </row>
     <row r="421" spans="1:4">
@@ -7111,7 +7111,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D421">
-        <v>0.4005769491195679</v>
+        <v>2.199542045593262</v>
       </c>
     </row>
     <row r="422" spans="1:4">
@@ -7125,7 +7125,7 @@
         <v>-1.899999976158142</v>
       </c>
       <c r="D422">
-        <v>1.472244262695312</v>
+        <v>1.488229751586914</v>
       </c>
     </row>
     <row r="423" spans="1:4">
@@ -7139,7 +7139,7 @@
         <v>8.600000381469727</v>
       </c>
       <c r="D423">
-        <v>3.064760208129883</v>
+        <v>2.233370542526245</v>
       </c>
     </row>
     <row r="424" spans="1:4">
@@ -7153,7 +7153,7 @@
         <v>1</v>
       </c>
       <c r="D424">
-        <v>0.5716065168380737</v>
+        <v>0.1332926899194717</v>
       </c>
     </row>
     <row r="425" spans="1:4">
@@ -7167,7 +7167,7 @@
         <v>-3.599999904632568</v>
       </c>
       <c r="D425">
-        <v>0.1266772449016571</v>
+        <v>-0.02462993562221527</v>
       </c>
     </row>
     <row r="426" spans="1:4">
@@ -7181,7 +7181,7 @@
         <v>5</v>
       </c>
       <c r="D426">
-        <v>2.986428499221802</v>
+        <v>2.931650400161743</v>
       </c>
     </row>
     <row r="427" spans="1:4">
@@ -7195,7 +7195,7 @@
         <v>-0.5</v>
       </c>
       <c r="D427">
-        <v>0.6083191633224487</v>
+        <v>0.1811912357807159</v>
       </c>
     </row>
     <row r="428" spans="1:4">
@@ -7209,7 +7209,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D428">
-        <v>-0.1125069260597229</v>
+        <v>-0.9116508960723877</v>
       </c>
     </row>
     <row r="429" spans="1:4">
@@ -7223,7 +7223,7 @@
         <v>7</v>
       </c>
       <c r="D429">
-        <v>2.595827341079712</v>
+        <v>2.208491563796997</v>
       </c>
     </row>
     <row r="430" spans="1:4">
@@ -7237,7 +7237,7 @@
         <v>-0.2000000029802322</v>
       </c>
       <c r="D430">
-        <v>2.195573568344116</v>
+        <v>3.472540855407715</v>
       </c>
     </row>
     <row r="431" spans="1:4">
@@ -7251,7 +7251,7 @@
         <v>-0.5</v>
       </c>
       <c r="D431">
-        <v>-0.3550586700439453</v>
+        <v>0.4719527661800385</v>
       </c>
     </row>
     <row r="432" spans="1:4">
@@ -7265,7 +7265,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D432">
-        <v>1.498168706893921</v>
+        <v>0.3576809167861938</v>
       </c>
     </row>
     <row r="433" spans="1:4">
@@ -7279,7 +7279,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D433">
-        <v>0.6247909665107727</v>
+        <v>0.9984084367752075</v>
       </c>
     </row>
     <row r="434" spans="1:4">
@@ -7293,7 +7293,7 @@
         <v>-3.799999952316284</v>
       </c>
       <c r="D434">
-        <v>-0.570428729057312</v>
+        <v>-0.140986829996109</v>
       </c>
     </row>
     <row r="435" spans="1:4">
@@ -7307,7 +7307,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D435">
-        <v>3.003308296203613</v>
+        <v>2.813515186309814</v>
       </c>
     </row>
     <row r="436" spans="1:4">
@@ -7321,7 +7321,7 @@
         <v>-0.5</v>
       </c>
       <c r="D436">
-        <v>-1.868803024291992</v>
+        <v>-1.554518699645996</v>
       </c>
     </row>
     <row r="437" spans="1:4">
@@ -7335,7 +7335,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D437">
-        <v>0.7601345777511597</v>
+        <v>0.472324550151825</v>
       </c>
     </row>
     <row r="438" spans="1:4">
@@ -7349,7 +7349,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D438">
-        <v>1.594481229782104</v>
+        <v>1.563771963119507</v>
       </c>
     </row>
     <row r="439" spans="1:4">
@@ -7363,7 +7363,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D439">
-        <v>0.3755488395690918</v>
+        <v>0.8999811410903931</v>
       </c>
     </row>
     <row r="440" spans="1:4">
@@ -7377,7 +7377,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D440">
-        <v>0.4672043919563293</v>
+        <v>0.2080139517784119</v>
       </c>
     </row>
     <row r="441" spans="1:4">
@@ -7391,7 +7391,7 @@
         <v>-1.700000047683716</v>
       </c>
       <c r="D441">
-        <v>-1.513029813766479</v>
+        <v>-0.3636306822299957</v>
       </c>
     </row>
     <row r="442" spans="1:4">
@@ -7405,7 +7405,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D442">
-        <v>0.8795642852783203</v>
+        <v>0.4782684743404388</v>
       </c>
     </row>
     <row r="443" spans="1:4">
@@ -7419,7 +7419,7 @@
         <v>5.300000190734863</v>
       </c>
       <c r="D443">
-        <v>3.699611902236938</v>
+        <v>3.732600927352905</v>
       </c>
     </row>
     <row r="444" spans="1:4">
@@ -7433,7 +7433,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D444">
-        <v>3.299714326858521</v>
+        <v>2.296388864517212</v>
       </c>
     </row>
     <row r="445" spans="1:4">
@@ -7447,7 +7447,7 @@
         <v>-1.700000047683716</v>
       </c>
       <c r="D445">
-        <v>-0.2421634793281555</v>
+        <v>0.6213041543960571</v>
       </c>
     </row>
     <row r="446" spans="1:4">
@@ -7461,7 +7461,7 @@
         <v>-3.200000047683716</v>
       </c>
       <c r="D446">
-        <v>-0.01742243766784668</v>
+        <v>0.04515334963798523</v>
       </c>
     </row>
     <row r="447" spans="1:4">
@@ -7475,7 +7475,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D447">
-        <v>0.4163372218608856</v>
+        <v>0.1153718531131744</v>
       </c>
     </row>
     <row r="448" spans="1:4">
@@ -7489,7 +7489,7 @@
         <v>6.800000190734863</v>
       </c>
       <c r="D448">
-        <v>3.082996606826782</v>
+        <v>5.333345413208008</v>
       </c>
     </row>
   </sheetData>
